--- a/demo/sol-internal/trackers-xlsx/Engagements.xlsx
+++ b/demo/sol-internal/trackers-xlsx/Engagements.xlsx
@@ -584,7 +584,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
